--- a/Figure 6/Figure 6-F.xlsx
+++ b/Figure 6/Figure 6-F.xlsx
@@ -5,27 +5,36 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A780B34-B1C7-463A-9F5E-9D90A0926B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9345F22-A06C-4D34-BB8E-09F1FA44C412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21530" yWindow="1790" windowWidth="19500" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>MUC1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,9 +63,6 @@
     <t>CON 5</t>
   </si>
   <si>
-    <t>CON 6</t>
-  </si>
-  <si>
     <t>ETEC 1</t>
   </si>
   <si>
@@ -72,9 +78,6 @@
     <t>ETEC 5</t>
   </si>
   <si>
-    <t>ETEC 6</t>
-  </si>
-  <si>
     <t>ETEC+WB800 1</t>
   </si>
   <si>
@@ -90,9 +93,6 @@
     <t>ETEC+WB800 5</t>
   </si>
   <si>
-    <t>ETEC+WB800 6</t>
-  </si>
-  <si>
     <t>ETEC+WB800_KR32 1</t>
   </si>
   <si>
@@ -106,9 +106,6 @@
   </si>
   <si>
     <t>ETEC+WB800_KR32 5</t>
-  </si>
-  <si>
-    <t>ETEC+WB800_KR32 6</t>
   </si>
 </sst>
 </file>
@@ -135,10 +132,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -163,7 +159,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -445,337 +441,294 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1">
-        <v>0.96172325409955661</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1.0978520186711134</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.93236974607739742</v>
+      <c r="B2" s="2">
+        <v>1.02404683867656</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2.7551072471157299</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1.5599198042637401</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1">
-        <v>0.82741942584690253</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0.57895143060053422</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.45411944251197989</v>
+      <c r="B3" s="2">
+        <v>1.3820207806470901</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.2913617900344101</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1.8468041482041</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="1">
-        <v>0.19682699414230109</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.25238029085699337</v>
+      <c r="B4" s="2">
+        <v>0.87683971387014403</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1.0215851670312901</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.87706331952474403</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1">
-        <v>0.82835220624688455</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.47740599880161622</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.72093731126663496</v>
+      <c r="B5" s="2">
+        <v>1.1033289568481099</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1.704794029191</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.80924050636761202</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1">
-        <v>0.73939677238004564</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.55166004951195069</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.64977533925757291</v>
+      <c r="B6" s="2">
+        <v>0.96422542490241003</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="2">
+        <v>0.94660593999125497</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
-        <v>0.73476975237684505</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0.69727501974850847</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.4819209962405997</v>
+      <c r="B7" s="2">
+        <v>0.87323809491162796</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.559270330280776</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.76638368844757998</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1">
-        <v>2.5667839179136958</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1.3057302863684073</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2.0515931284599347</v>
+      <c r="B8" s="2">
+        <v>0.67652207272711795</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.993649866915991</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.99625063153508198</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="1">
-        <v>1.1643082943295986</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1.0768589974546348</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.97684807757008085</v>
+      <c r="B9" s="2">
+        <v>0.86774768023615501</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.87943762598707098</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.78424779049040705</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1">
-        <v>0.92361540593178515</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="2">
+        <v>0.78205799824231104</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1.25015630085533</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.70467545958576605</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="1">
-        <v>0.86052475454628286</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.61819079285738832</v>
+      <c r="B11" s="2">
+        <v>0.67597751868456502</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="2">
+        <v>0.66514698630791003</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1">
-        <v>0.94163654950146847</v>
-      </c>
-      <c r="D12" s="1">
-        <v>0.60706515459238974</v>
+      <c r="B12" s="2">
+        <v>0.71615738692350694</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.89982232364685</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.50579895991659396</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="1">
-        <v>1.0995741305356823</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0.67531352673683465</v>
-      </c>
-      <c r="D13" s="1">
-        <v>0.6228119636351791</v>
+      <c r="B13" s="2">
+        <v>0.82679502140711703</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1.2589823138065901</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.69094174107057005</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="1">
-        <v>0.7820266372683965</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1.327695843079046</v>
-      </c>
-      <c r="D14" s="2"/>
+      <c r="B14" s="2">
+        <v>0.796386008021856</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1.0147698473167099</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.96089605856604399</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="1">
-        <v>0.98580035810302369</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1">
-        <v>0.92821629348147838</v>
+      <c r="B15" s="2">
+        <v>0.70806940916053995</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1.2775733924392001</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.56712752868042704</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="1">
-        <v>0.68573140168141944</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0.80083497634971557</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1.183067941307713</v>
+      <c r="B16" s="2">
+        <v>1.00261077482491</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="2">
+        <v>0.68855100027702298</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="1">
-        <v>0.95087460731679452</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0.51509310986141466</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0.75348962389134966</v>
+      <c r="B17" s="2">
+        <v>0.84401907428723</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.84432105791197798</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.85770291619776096</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="1">
-        <v>0.53076486071599172</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0.62906123811075587</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1.0753933530161173</v>
+      <c r="B18" s="2">
+        <v>0.87651310180520303</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1.6421352269599701</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.92204682520617598</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="1">
-        <v>0.78283662046560742</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0.93752692377552582</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0.97807990827743418</v>
+      <c r="B19" s="2">
+        <v>0.78205799824231004</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.69690755104699798</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1.0486621316373299</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="1">
-        <v>1.3753508570044657</v>
-      </c>
-      <c r="C20" s="1">
-        <v>2.6122699787312119E-4</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0.70071888994183285</v>
+      <c r="B20" s="2">
+        <v>0.76844579506208199</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1.1114494825213399</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.81130610458721497</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="1">
-        <v>0.68618411310944749</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0.61057436636275342</v>
-      </c>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1">
-        <v>0.64976241871989426</v>
-      </c>
-      <c r="D22" s="1"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="1">
-        <v>0.54353844228327775</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1.1204027703417334</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0.53281305013980407</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1">
-        <v>1.1377417023081093</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0.93949790470017769</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1.3453172182888327</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.7639309926306892</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0.88106905949443681</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0.30766890824888354</v>
+      <c r="B21" s="2">
+        <v>0.75892862950604301</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="2">
+        <v>0.93882223870595605</v>
       </c>
     </row>
   </sheetData>
